--- a/docs/data/jp/xlsx/5280.xlsx
+++ b/docs/data/jp/xlsx/5280.xlsx
@@ -10054,7 +10054,7 @@
     <row r="119">
       <c r="A119" s="18" t="inlineStr">
         <is>
-          <t>Refund Of Real Estate Acquisition Taxes NOI</t>
+          <t>부동산 취득세 환급금</t>
         </is>
       </c>
       <c r="C119" s="20" t="n">
@@ -14910,7 +14910,7 @@
     <row r="213">
       <c r="A213" s="18" t="inlineStr">
         <is>
-          <t>LeasingAndManagementReportableSegmentsMember · Operating Income</t>
+          <t>LeasingAndManagementReportableSegmentsMember · 부문 이익 또는 손실(△)</t>
         </is>
       </c>
       <c r="I213" s="20" t="n">
@@ -16305,7 +16305,7 @@
     <row r="242">
       <c r="A242" s="18" t="inlineStr">
         <is>
-          <t>Loss On Valuation Of Real Estate For Sale Ope CF</t>
+          <t>판매용 부동산 평가손</t>
         </is>
       </c>
       <c r="D242" s="20" t="n">
@@ -16579,7 +16579,7 @@
     <row r="249">
       <c r="A249" s="18" t="inlineStr">
         <is>
-          <t>Gain On Cancellation Of Guarantee Deposited Ope CF</t>
+          <t>예수 보증금 등 해약 이익</t>
         </is>
       </c>
       <c r="P249" s="20" t="n">
@@ -18191,7 +18191,7 @@
     <row r="286">
       <c r="A286" s="18" t="inlineStr">
         <is>
-          <t>Proceeds From Withdrawal Of Investments In Silent Partnership Inv CF</t>
+          <t>익명조합 출자금 환급 수입</t>
         </is>
       </c>
       <c r="D286" s="20" t="n">
@@ -21854,7 +21854,7 @@
     <row r="79">
       <c r="A79" s="18" t="inlineStr">
         <is>
-          <t>Real Estate For Sale In Trust CA</t>
+          <t>신탁 판매용 부동산</t>
         </is>
       </c>
       <c r="C79" s="20" t="n">
